--- a/docs/assets/3rdparty/source/icecream-flavours-all-curated-definitions.xlsx
+++ b/docs/assets/3rdparty/source/icecream-flavours-all-curated-definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leskneebone/Projects/docs/docs/assets/3rdparty/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{004FEADD-720D-EF40-961A-E9A57003C1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042D150F-F5AE-ED43-A756-E3237612802D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="2520" windowWidth="27640" windowHeight="16600" xr2:uid="{D8F5B238-1CA9-2345-B0A6-1E95D04ABAF3}"/>
+    <workbookView xWindow="820" yWindow="720" windowWidth="27640" windowHeight="16600" xr2:uid="{D8F5B238-1CA9-2345-B0A6-1E95D04ABAF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="207">
   <si>
     <t>Banana</t>
   </si>
@@ -398,120 +398,60 @@
     <t xml:space="preserve">Lúcuma </t>
   </si>
   <si>
-    <t xml:space="preserve"> a popular Peruvian ice cream flavor with an orange color and a sweet nutty taste</t>
-  </si>
-  <si>
     <t xml:space="preserve">Moon mist </t>
   </si>
   <si>
-    <t xml:space="preserve"> a blend of grape, banana, and blue raspberry (or sometimes bubblegum) flavors, popular in Atlantic Canada. The flavors are generally blended together to give a mist-like texture.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Raspberry ripple </t>
   </si>
   <si>
-    <t xml:space="preserve"> consists of raspberry syrup injected into vanilla ice cream.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tiger tail </t>
   </si>
   <si>
-    <t xml:space="preserve"> a flavor popular in Canada, consisting of orange-flavored ice cream with swirls of black licorice</t>
-  </si>
-  <si>
     <t xml:space="preserve">Biscuit Tortoni </t>
   </si>
   <si>
-    <t xml:space="preserve"> an ice cream made with eggs and heavy cream, often containing chopped cherries or topped with minced almonds or crumbled macaroons</t>
-  </si>
-  <si>
     <t xml:space="preserve">Blue moon </t>
   </si>
   <si>
-    <t xml:space="preserve"> an ice cream flavor with bright blue coloring, available in the Upper Midwest of the United States</t>
-  </si>
-  <si>
     <t xml:space="preserve">Butter Brickle </t>
   </si>
   <si>
-    <t xml:space="preserve"> the registered trademark of a toffee ice cream flavoring and of a toffee-centered chocolate-covered candy bar similar to the Heath bar, introduced by the Blackstone Hotel in Omaha, Nebraska, in the 1920s. Alternately, it is often prepared and sold as butter vanilla-flavored ice cream with tiny flecks of butter toffee instead of chunks of Heath bar.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Butter pecan </t>
   </si>
   <si>
-    <t xml:space="preserve"> a smooth vanilla ice cream with a slight buttery flavor, with pecans added.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chocolate chip </t>
   </si>
   <si>
-    <t xml:space="preserve"> vanilla base, with chunks of solid chocolate. Declining in popularity in the 2020s. Sometimes chocolate ice cream was used, which was usually called "Chocolate chocolate chip"</t>
-  </si>
-  <si>
     <t xml:space="preserve">Goody Goody Gum Drops </t>
   </si>
   <si>
-    <t xml:space="preserve"> unique to New Zealand</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hokey pokey </t>
   </si>
   <si>
-    <t xml:space="preserve"> a flavor of ice cream in New Zealand, consisting of plain vanilla ice cream with small, solid lumps of honeycomb toffee</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mint chocolate chip </t>
   </si>
   <si>
-    <t xml:space="preserve"> composed of mint ice cream with small chocolate chips. In some cases the liqueur crème de menthe is used to provide the mint flavor, but in most cases peppermint or spearmint flavoring is used.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Neapolitan </t>
   </si>
   <si>
-    <t xml:space="preserve"> composed of vanilla, chocolate and strawberry ice cream together side by side</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rocky road </t>
   </si>
   <si>
-    <t xml:space="preserve"> although there are variations from the original flavor, it is traditionally composed of chocolate ice cream, nuts, and whole or diced marshmallows, or sometimes replaced with marshmallow creme, a more fluid version</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spumoni </t>
   </si>
   <si>
-    <t xml:space="preserve"> a molded Italian ice cream made with layers of different colors and flavors, usually containing candied fruits and nuts.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tramontana </t>
   </si>
   <si>
-    <t xml:space="preserve"> composed of dark chocolate, white chocolate, dulce de leche and cookies.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bacon </t>
   </si>
   <si>
-    <t xml:space="preserve"> a modern invention, generally created by adding bacon to egg custard and freezing the mixture</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crab </t>
   </si>
   <si>
-    <t xml:space="preserve"> a Japanese creation,it is described as having a sweet taste; the island of Hokkaido, Japan, is known for manufacturing it</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spundekas </t>
   </si>
   <si>
-    <t xml:space="preserve"> based on the German cream cheese of the same name</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> a popular ice cream flavor in the Philippines</t>
-  </si>
-  <si>
     <t>Definitions</t>
   </si>
   <si>
@@ -570,6 +510,156 @@
   </si>
   <si>
     <t>Coffee ice cream is an ice cream flavor made with coffee or coffee flavoring.</t>
+  </si>
+  <si>
+    <t>Butterscotch ice cream flavor</t>
+  </si>
+  <si>
+    <t>Bubblegum ice cream flavor</t>
+  </si>
+  <si>
+    <t>Tutti frutti ice cream flavor</t>
+  </si>
+  <si>
+    <t>Cake batter ice cream flavor</t>
+  </si>
+  <si>
+    <t>Caramel ice cream flavor</t>
+  </si>
+  <si>
+    <t>Chocolate chip cookie dough ice cream flavor</t>
+  </si>
+  <si>
+    <t>Cookies and cream ice cream flavor</t>
+  </si>
+  <si>
+    <t>Cotton candy ice cream flavor</t>
+  </si>
+  <si>
+    <t>Dulce de leche ice cream flavor</t>
+  </si>
+  <si>
+    <t>Earl Grey tea ice cream flavor</t>
+  </si>
+  <si>
+    <t>Eggnog ice cream flavor</t>
+  </si>
+  <si>
+    <t>French vanilla ice cream flavor</t>
+  </si>
+  <si>
+    <t>Green tea  ice cream flavor</t>
+  </si>
+  <si>
+    <t>Halva ice cream flavor</t>
+  </si>
+  <si>
+    <t>Maple ice cream flavor</t>
+  </si>
+  <si>
+    <t>Moose tracks ice cream flavor</t>
+  </si>
+  <si>
+    <t>Pistachio ice cream flavor</t>
+  </si>
+  <si>
+    <t>Peanut butter ice cream flavor</t>
+  </si>
+  <si>
+    <t>Rose ice cream flavor</t>
+  </si>
+  <si>
+    <t>Stracciatella ice cream flavor</t>
+  </si>
+  <si>
+    <t>Thai tea ice cream flavor</t>
+  </si>
+  <si>
+    <t>Vanilla ice cream flavor</t>
+  </si>
+  <si>
+    <t>Beer ice cream flavor</t>
+  </si>
+  <si>
+    <t>Carrot ice cream flavor</t>
+  </si>
+  <si>
+    <t>Cheese ice cream flavor</t>
+  </si>
+  <si>
+    <t>Creole cream cheese ice cream flavor</t>
+  </si>
+  <si>
+    <t>Garlic ice cream flavor</t>
+  </si>
+  <si>
+    <t>Oyster ice cream flavor</t>
+  </si>
+  <si>
+    <t>Korean Sweet corn ice cream flavor</t>
+  </si>
+  <si>
+    <t>Taro ice cream flavor</t>
+  </si>
+  <si>
+    <t>a flavor of ice cream in New Zealand, consisting of plain vanilla ice cream with small, solid lumps of honeycomb toffee</t>
+  </si>
+  <si>
+    <t>Goody Goody Gum Drops ice cream flavor, unique to New Zealand</t>
+  </si>
+  <si>
+    <t>Vanilla base, with chunks of solid chocolate. Declining in popularity in the 2020s. Sometimes chocolate ice cream was used, which was usually called "Chocolate chocolate chip"</t>
+  </si>
+  <si>
+    <t>A flavor popular in Canada, consisting of orange-flavored ice cream with swirls of black licorice</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Consists of raspberry syrup injected into vanilla ice cream.</t>
+  </si>
+  <si>
+    <t>A blend of grape, banana, and blue raspberry (or sometimes bubblegum) flavors, popular in Atlantic Canada. The flavors are generally blended together to give a mist-like texture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A popular Peruvian ice cream flavor with an orange color and a sweet nutty taste</t>
+  </si>
+  <si>
+    <t>An ice cream made with eggs and heavy cream, often containing chopped cherries or topped with minced almonds or crumbled macaroons</t>
+  </si>
+  <si>
+    <t>An ice cream flavor with bright blue coloring, available in the Upper Midwest of the United States</t>
+  </si>
+  <si>
+    <t>The registered trademark of a toffee ice cream flavoring and of a toffee-centered chocolate-covered candy bar similar to the Heath bar, introduced by the Blackstone Hotel in Omaha, Nebraska, in the 1920s. Alternately, it is often prepared and sold as butter vanilla-flavored ice cream with tiny flecks of butter toffee instead of chunks of Heath bar.</t>
+  </si>
+  <si>
+    <t>A smooth vanilla ice cream with a slight buttery flavor, with pecans added.</t>
+  </si>
+  <si>
+    <t>Composed of mint ice cream with small chocolate chips. In some cases the liqueur crème de menthe is used to provide the mint flavor, but in most cases peppermint or spearmint flavoring is used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Composed of vanilla, chocolate and strawberry ice cream together side by side</t>
+  </si>
+  <si>
+    <t>Although there are variations from the original flavor, it is traditionally composed of chocolate ice cream, nuts, and whole or diced marshmallows, or sometimes replaced with marshmallow creme, a more fluid version</t>
+  </si>
+  <si>
+    <t>A molded Italian ice cream made with layers of different colors and flavors, usually containing candied fruits and nuts.</t>
+  </si>
+  <si>
+    <t>Composed of dark chocolate, white chocolate, dulce de leche and cookies.</t>
+  </si>
+  <si>
+    <t>A modern invention, generally created by adding bacon to egg custard and freezing the mixture</t>
+  </si>
+  <si>
+    <t>A Japanese creation,it is described as having a sweet taste; the island of Hokkaido, Japan, is known for manufacturing it</t>
+  </si>
+  <si>
+    <t>Ice cream flavor based on the German cream cheese of the same name</t>
+  </si>
+  <si>
+    <t>A popular ice cream flavor in the Philippines</t>
   </si>
 </sst>
 </file>
@@ -970,10 +1060,10 @@
         <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D1" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -994,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1005,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1016,10 +1106,10 @@
         <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1030,7 +1120,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1041,7 +1131,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1052,7 +1142,7 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>119</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1074,7 +1164,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1082,10 +1172,10 @@
         <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -1096,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1107,7 +1197,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -1115,10 +1205,10 @@
         <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1129,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1140,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1151,7 +1241,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1162,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1173,7 +1263,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1181,10 +1271,10 @@
         <v>67</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1195,7 +1285,7 @@
         <v>13</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1224,10 +1314,10 @@
         <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1235,10 +1325,10 @@
         <v>71</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1249,7 +1339,7 @@
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1257,10 +1347,10 @@
         <v>73</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1271,7 +1361,7 @@
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -1279,10 +1369,10 @@
         <v>75</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1293,7 +1383,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1304,7 +1394,7 @@
         <v>18</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1315,7 +1405,7 @@
         <v>19</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1323,10 +1413,10 @@
         <v>79</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -1337,7 +1427,7 @@
         <v>20</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -1348,7 +1438,7 @@
         <v>21</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -1359,7 +1449,7 @@
         <v>22</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -1370,7 +1460,7 @@
         <v>23</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -1381,7 +1471,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -1392,7 +1482,7 @@
         <v>25</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -1403,7 +1493,7 @@
         <v>26</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -1414,7 +1504,7 @@
         <v>27</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>27</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -1422,10 +1512,10 @@
         <v>88</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -1436,7 +1526,7 @@
         <v>28</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -1447,7 +1537,7 @@
         <v>29</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -1455,10 +1545,10 @@
         <v>91</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -1469,7 +1559,7 @@
         <v>30</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -1477,10 +1567,10 @@
         <v>93</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -1491,7 +1581,7 @@
         <v>31</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -1499,10 +1589,10 @@
         <v>95</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -1513,7 +1603,7 @@
         <v>32</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>32</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1524,7 +1614,7 @@
         <v>33</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -1532,10 +1622,10 @@
         <v>98</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -1546,7 +1636,7 @@
         <v>34</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>34</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -1554,10 +1644,10 @@
         <v>100</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -1568,7 +1658,7 @@
         <v>35</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -1579,7 +1669,7 @@
         <v>36</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -1587,10 +1677,10 @@
         <v>103</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>149</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -1601,7 +1691,7 @@
         <v>37</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -1619,10 +1709,10 @@
         <v>105</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -1633,7 +1723,7 @@
         <v>38</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>38</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -1644,7 +1734,7 @@
         <v>39</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -1655,7 +1745,7 @@
         <v>40</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -1663,10 +1753,10 @@
         <v>109</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>153</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -1677,7 +1767,7 @@
         <v>41</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -1688,7 +1778,7 @@
         <v>42</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -1699,7 +1789,7 @@
         <v>43</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -1710,7 +1800,7 @@
         <v>44</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -1721,7 +1811,7 @@
         <v>45</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -1729,10 +1819,10 @@
         <v>115</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -1740,16 +1830,17 @@
         <v>116</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="D74" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/docs/assets/3rdparty/source/icecream-flavours-all-curated-definitions.xlsx
+++ b/docs/assets/3rdparty/source/icecream-flavours-all-curated-definitions.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="211">
   <si>
     <t>Banana</t>
   </si>
@@ -191,205 +191,205 @@
     <t>FLAVOR NAMES</t>
   </si>
   <si>
-    <t>icf:45b0a9d3-d3c9-4c19-b4ef-0511a8827101</t>
-  </si>
-  <si>
-    <t>icf:abf359ff-5c42-42e1-91a5-21973879f6f0</t>
-  </si>
-  <si>
-    <t>icf:0f748e6f-ae0b-49a9-bac9-98db1de6fd04</t>
-  </si>
-  <si>
-    <t>icf:bf94fff7-9ef5-4af6-91dc-bf332e1bbd72</t>
-  </si>
-  <si>
-    <t>icf:556b0f61-f107-4519-8bbe-cf3c29d840bb</t>
-  </si>
-  <si>
-    <t>icf:79aaa965-5e88-4a01-8b5a-87438ff46cf6</t>
-  </si>
-  <si>
-    <t>icf:4343af06-9db2-43d4-920a-61d349ef42f5</t>
-  </si>
-  <si>
-    <t>icf:f476202a-b952-4b55-8877-33570ee26cf5</t>
-  </si>
-  <si>
-    <t>icf:cd2071b4-cb2e-4c12-ad82-fa7b2c844899</t>
-  </si>
-  <si>
-    <t>icf:61ed4c66-f7d8-40c9-8866-cc4bdee3ea44</t>
-  </si>
-  <si>
-    <t>icf:9e8afe4c-f6db-40e3-a625-7dbeadc1a3d5</t>
-  </si>
-  <si>
-    <t>icf:a5120bb8-2a39-4b7e-95e4-c05646ab53e2</t>
-  </si>
-  <si>
-    <t>icf:7b276e8c-ac83-4eb0-8b8d-e26f0f00d190</t>
-  </si>
-  <si>
-    <t>icf:ccb7b867-4f44-4eea-bd09-99f964664733</t>
-  </si>
-  <si>
-    <t>icf:b8af11ac-39c5-4547-8ff0-1cb77e50f9d5</t>
-  </si>
-  <si>
-    <t>icf:bd9289fa-9715-4a2e-89bd-bc4f705dc167</t>
-  </si>
-  <si>
-    <t>icf:0e9b17d8-339c-4a55-8157-03b15be56f76</t>
-  </si>
-  <si>
-    <t>icf:d35b1641-f112-4ab5-83fe-95e98229f4e7</t>
-  </si>
-  <si>
-    <t>icf:a1a144fd-3f41-4961-9bb1-47ac783232b5</t>
-  </si>
-  <si>
-    <t>icf:9de1e781-4733-4cbe-8cb2-143d7a4ed92f</t>
-  </si>
-  <si>
-    <t>icf:e702da60-1dbe-48ee-891f-e1de99ee07d5</t>
-  </si>
-  <si>
-    <t>icf:2f524245-e21c-4c02-966d-f3b4022535ea</t>
-  </si>
-  <si>
-    <t>icf:c4c2344c-4b1b-462a-b9f9-e1b03faeb0dd</t>
-  </si>
-  <si>
-    <t>icf:f4fe093d-96d6-4419-8079-1fdba8a479cc</t>
-  </si>
-  <si>
-    <t>icf:66dcdd54-fffb-4d29-90bc-0be9a9d052b5</t>
-  </si>
-  <si>
-    <t>icf:a61185c1-786a-4a93-8964-0d53686baddd</t>
-  </si>
-  <si>
-    <t>icf:aa64a8c2-8dbb-428b-94f9-fc328870d3ec</t>
-  </si>
-  <si>
-    <t>icf:2307a8fb-e802-403a-b255-6ec1a57677aa</t>
-  </si>
-  <si>
-    <t>icf:e8555003-5203-47d4-af04-70798add66ad</t>
-  </si>
-  <si>
-    <t>icf:f7bbc944-ecdc-4517-8f71-6ac6653db5c4</t>
-  </si>
-  <si>
-    <t>icf:678299ea-ae67-4736-b109-02f3b5c2e752</t>
-  </si>
-  <si>
-    <t>icf:cd7ecf43-79b3-4495-98a5-fea33b86a29c</t>
-  </si>
-  <si>
-    <t>icf:10cdc74f-c236-42cf-bb32-33f40c882189</t>
-  </si>
-  <si>
-    <t>icf:1619cc1c-c75b-45d1-bdaf-ced29978673f</t>
-  </si>
-  <si>
-    <t>icf:bbe41b1a-5eb1-4d35-af25-673b0c0c842d</t>
-  </si>
-  <si>
-    <t>icf:98656441-5fd4-42e8-bd11-cfce8fae4a86</t>
-  </si>
-  <si>
-    <t>icf:6148a62f-1ae4-4797-9f6a-359f17c2c60a</t>
-  </si>
-  <si>
-    <t>icf:f8892819-70b5-4efc-8e42-43d1024d943e</t>
-  </si>
-  <si>
-    <t>icf:d4ef5ab1-2fd4-4b70-b7a0-ad79605f5e4e</t>
-  </si>
-  <si>
-    <t>icf:5c2bad30-3036-4394-abef-1daf0cb6351d</t>
-  </si>
-  <si>
-    <t>icf:07ff3c57-c075-4a95-be6a-99955621dd5c</t>
-  </si>
-  <si>
-    <t>icf:3c71c026-00b2-435e-bb8b-66d006e7b133</t>
-  </si>
-  <si>
-    <t>icf:ade1b5f0-58c6-46a8-8faa-6ed4224c72b7</t>
-  </si>
-  <si>
-    <t>icf:23798250-a926-42ba-95ce-c5576efa0bec</t>
-  </si>
-  <si>
-    <t>icf:a886dea1-e597-40a2-84c2-f91f1750c724</t>
-  </si>
-  <si>
-    <t>icf:06f52b88-9ad0-4214-bf41-f5c23514d2cd</t>
-  </si>
-  <si>
-    <t>icf:28d8e6bb-6003-451e-b21e-292b4c5067f4</t>
-  </si>
-  <si>
-    <t>icf:48493fe1-dccb-45d0-9082-90ee9cb2e2f6</t>
-  </si>
-  <si>
-    <t>icf:cf5e8785-f0d9-4d8f-bcd8-c196b3751051</t>
-  </si>
-  <si>
-    <t>icf:a91c45b3-4168-4326-ba6f-6300858fde67</t>
-  </si>
-  <si>
-    <t>icf:a06e660a-7ca5-4213-88a9-5c2ea3574899</t>
-  </si>
-  <si>
-    <t>icf:8f32f706-4827-4b52-8658-97af4cfa0398</t>
-  </si>
-  <si>
-    <t>icf:295b3fc1-a889-4960-bdbd-304392d1f0ec</t>
-  </si>
-  <si>
-    <t>icf:033da6cd-a916-467c-bbea-a6cd7b2fd9a3</t>
-  </si>
-  <si>
-    <t>icf:f8463b04-fa44-41b7-bb42-acc83a089cbb</t>
-  </si>
-  <si>
-    <t>icf:cc6b3ba1-b7ef-4ea9-b60a-77c52c1bb74d</t>
-  </si>
-  <si>
-    <t>icf:e54eea7d-074b-4d7b-8d73-d0df22b1f3e3</t>
-  </si>
-  <si>
-    <t>icf:2db0fe98-c26f-4cde-955e-53e0cbe5ee8e</t>
-  </si>
-  <si>
-    <t>icf:abb0e61b-5c54-4984-a13b-780563887653</t>
-  </si>
-  <si>
-    <t>icf:f550c468-b125-49ff-a3f2-1876954f7f73</t>
-  </si>
-  <si>
-    <t>icf:1671e56f-52db-48af-a0a5-e45f8eb66053</t>
-  </si>
-  <si>
-    <t>icf:88947dcc-ef36-4bda-b26f-d91b9bbb92d9</t>
-  </si>
-  <si>
-    <t>icf:b868d0d7-e574-48b0-a6b2-433a01c7434a</t>
-  </si>
-  <si>
-    <t>icf:b023c80a-7d05-4324-8207-4e5bba5dec17</t>
-  </si>
-  <si>
-    <t>icf:96e04174-022b-4934-a431-3bb3f96f015f</t>
-  </si>
-  <si>
-    <t>icf:392def8f-2e32-4c23-ae4f-2f149787f3a6</t>
-  </si>
-  <si>
-    <t>icf:8e63e629-3b8f-47d7-86d8-079bc74dc92c</t>
+    <t>icf:2</t>
+  </si>
+  <si>
+    <t>icf:3</t>
+  </si>
+  <si>
+    <t>icf:4</t>
+  </si>
+  <si>
+    <t>icf:5</t>
+  </si>
+  <si>
+    <t>icf:6</t>
+  </si>
+  <si>
+    <t>icf:7</t>
+  </si>
+  <si>
+    <t>icf:8</t>
+  </si>
+  <si>
+    <t>icf:9</t>
+  </si>
+  <si>
+    <t>icf:10</t>
+  </si>
+  <si>
+    <t>icf:11</t>
+  </si>
+  <si>
+    <t>icf:12</t>
+  </si>
+  <si>
+    <t>icf:13</t>
+  </si>
+  <si>
+    <t>icf:14</t>
+  </si>
+  <si>
+    <t>icf:15</t>
+  </si>
+  <si>
+    <t>icf:16</t>
+  </si>
+  <si>
+    <t>icf:17</t>
+  </si>
+  <si>
+    <t>icf:18</t>
+  </si>
+  <si>
+    <t>icf:19</t>
+  </si>
+  <si>
+    <t>icf:20</t>
+  </si>
+  <si>
+    <t>icf:21</t>
+  </si>
+  <si>
+    <t>icf:23</t>
+  </si>
+  <si>
+    <t>icf:24</t>
+  </si>
+  <si>
+    <t>icf:25</t>
+  </si>
+  <si>
+    <t>icf:26</t>
+  </si>
+  <si>
+    <t>icf:27</t>
+  </si>
+  <si>
+    <t>icf:28</t>
+  </si>
+  <si>
+    <t>icf:29</t>
+  </si>
+  <si>
+    <t>icf:30</t>
+  </si>
+  <si>
+    <t>icf:31</t>
+  </si>
+  <si>
+    <t>icf:32</t>
+  </si>
+  <si>
+    <t>icf:33</t>
+  </si>
+  <si>
+    <t>icf:34</t>
+  </si>
+  <si>
+    <t>icf:35</t>
+  </si>
+  <si>
+    <t>icf:36</t>
+  </si>
+  <si>
+    <t>icf:37</t>
+  </si>
+  <si>
+    <t>icf:38</t>
+  </si>
+  <si>
+    <t>icf:39</t>
+  </si>
+  <si>
+    <t>icf:40</t>
+  </si>
+  <si>
+    <t>icf:41</t>
+  </si>
+  <si>
+    <t>icf:42</t>
+  </si>
+  <si>
+    <t>icf:43</t>
+  </si>
+  <si>
+    <t>icf:44</t>
+  </si>
+  <si>
+    <t>icf:45</t>
+  </si>
+  <si>
+    <t>icf:46</t>
+  </si>
+  <si>
+    <t>icf:47</t>
+  </si>
+  <si>
+    <t>icf:48</t>
+  </si>
+  <si>
+    <t>icf:49</t>
+  </si>
+  <si>
+    <t>icf:50</t>
+  </si>
+  <si>
+    <t>icf:51</t>
+  </si>
+  <si>
+    <t>icf:52</t>
+  </si>
+  <si>
+    <t>icf:53</t>
+  </si>
+  <si>
+    <t>icf:54</t>
+  </si>
+  <si>
+    <t>icf:55</t>
+  </si>
+  <si>
+    <t>icf:56</t>
+  </si>
+  <si>
+    <t>icf:57</t>
+  </si>
+  <si>
+    <t>icf:59</t>
+  </si>
+  <si>
+    <t>icf:60</t>
+  </si>
+  <si>
+    <t>icf:61</t>
+  </si>
+  <si>
+    <t>icf:62</t>
+  </si>
+  <si>
+    <t>icf:63</t>
+  </si>
+  <si>
+    <t>icf:64</t>
+  </si>
+  <si>
+    <t>icf:65</t>
+  </si>
+  <si>
+    <t>icf:66</t>
+  </si>
+  <si>
+    <t>icf:67</t>
+  </si>
+  <si>
+    <t>icf:68</t>
+  </si>
+  <si>
+    <t>icf:69</t>
+  </si>
+  <si>
+    <t>icf:70</t>
   </si>
   <si>
     <t xml:space="preserve">Cherry </t>
@@ -660,6 +660,18 @@
   </si>
   <si>
     <t>A popular ice cream flavor in the Philippines</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>icf:1</t>
+  </si>
+  <si>
+    <t>icf:22</t>
+  </si>
+  <si>
+    <t>icf:58</t>
   </si>
 </sst>
 </file>
@@ -1045,9 +1057,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
   <dimension ref="A1:D74"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
     <col min="2" max="2" width="35.1640625" customWidth="1"/>
@@ -1055,7 +1067,10 @@
     <col min="4" max="4" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ns3:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>207</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1066,17 +1081,21 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ns3:dyDescent="0.2">
+      <c r="A2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ns3:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>208</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -1087,7 +1106,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1098,7 +1117,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -1112,7 +1131,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -1123,7 +1142,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -1134,7 +1153,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ns3:dyDescent="0.2">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1145,7 +1164,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ns3:dyDescent="0.2">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1167,7 +1186,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ns3:dyDescent="0.2">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1178,7 +1197,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1189,7 +1208,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -1200,7 +1219,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -1211,7 +1230,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1222,7 +1241,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ns3:dyDescent="0.2">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -1233,7 +1252,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ns3:dyDescent="0.2">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1244,7 +1263,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ns3:dyDescent="0.2">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -1255,7 +1274,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -1266,7 +1285,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -1277,7 +1296,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -1288,7 +1307,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ns3:dyDescent="0.2">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -1299,17 +1318,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ns3:dyDescent="0.2">
+      <c r="A24"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ns3:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>209</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ns3:dyDescent="0.2">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -1320,7 +1343,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -1331,7 +1354,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ns3:dyDescent="0.2">
       <c r="A28" t="s">
         <v>72</v>
       </c>
@@ -1342,7 +1365,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>73</v>
       </c>
@@ -1353,7 +1376,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -1364,7 +1387,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1375,7 +1398,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1386,7 +1409,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -1397,7 +1420,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ns3:dyDescent="0.2">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1408,7 +1431,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1419,7 +1442,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -1430,7 +1453,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -1441,7 +1464,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -1452,7 +1475,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>83</v>
       </c>
@@ -1463,7 +1486,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ns3:dyDescent="0.2">
       <c r="A40" t="s">
         <v>84</v>
       </c>
@@ -1474,7 +1497,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1485,7 +1508,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1496,7 +1519,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1507,7 +1530,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -1518,7 +1541,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -1529,7 +1552,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ns3:dyDescent="0.2">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -1540,7 +1563,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ns3:dyDescent="0.2">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -1551,7 +1574,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ns3:dyDescent="0.2">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -1562,7 +1585,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ns3:dyDescent="0.2">
       <c r="A49" t="s">
         <v>93</v>
       </c>
@@ -1573,7 +1596,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -1584,7 +1607,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>95</v>
       </c>
@@ -1595,7 +1618,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -1606,7 +1629,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>97</v>
       </c>
@@ -1617,7 +1640,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ns3:dyDescent="0.2">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -1628,7 +1651,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>99</v>
       </c>
@@ -1639,7 +1662,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>100</v>
       </c>
@@ -1650,7 +1673,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>101</v>
       </c>
@@ -1661,7 +1684,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>102</v>
       </c>
@@ -1672,7 +1695,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>103</v>
       </c>
@@ -1683,7 +1706,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ns3:dyDescent="0.2">
       <c r="A60" t="s">
         <v>104</v>
       </c>
@@ -1694,17 +1717,21 @@
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ns3:dyDescent="0.2">
+      <c r="A61"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ns3:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>210</v>
+      </c>
       <c r="B62" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ns3:dyDescent="0.2">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -1715,7 +1742,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>106</v>
       </c>
@@ -1726,7 +1753,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>107</v>
       </c>
@@ -1737,7 +1764,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>108</v>
       </c>
@@ -1748,7 +1775,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>109</v>
       </c>
@@ -1759,7 +1786,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>110</v>
       </c>
@@ -1770,7 +1797,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>111</v>
       </c>
@@ -1781,7 +1808,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1792,7 +1819,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>113</v>
       </c>
@@ -1803,7 +1830,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ns3:dyDescent="0.2">
       <c r="A72" t="s">
         <v>114</v>
       </c>
@@ -1814,7 +1841,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ns3:dyDescent="0.2">
       <c r="A73" t="s">
         <v>115</v>
       </c>
@@ -1825,10 +1852,8 @@
         <v>205</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>116</v>
-      </c>
+    <row r="74" spans="1:4" ns3:dyDescent="0.2">
+      <c r="A74"/>
       <c r="B74" s="2" t="s">
         <v>141</v>
       </c>
